--- a/files/港岛-赤柱-One stanley.xlsx
+++ b/files/港岛-赤柱-One stanley.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -3728,7 +3728,7 @@
           <t>C | 2452呎 (4+房)
 $8,620万
 $35,155/呎
-(26年-06月)</t>
+(已售)</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">

--- a/files/港岛-赤柱-One stanley.xlsx
+++ b/files/港岛-赤柱-One stanley.xlsx
@@ -8,17 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座 销控表" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座 销控表" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座 销控表" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座 销控表" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -121,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -186,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -202,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -613,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -718,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -764,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -902,7 +753,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -948,7 +799,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1044,7 +895,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1090,7 +941,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1136,7 +987,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1182,7 +1033,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1228,7 +1079,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1274,7 +1125,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1320,7 +1171,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1366,7 +1217,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1412,7 +1263,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1458,7 +1309,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1504,7 +1355,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1550,7 +1401,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1796,7 +1647,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1942,7 +1793,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2038,7 +1889,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2084,7 +1935,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2130,7 +1981,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2226,7 +2077,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2272,7 +2123,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2318,7 +2169,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2364,7 +2215,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2560,7 +2411,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2806,7 +2657,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2902,7 +2753,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2948,7 +2799,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2994,7 +2845,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3056,6 +2907,1538 @@
       <c r="J52" s="3" t="inlineStr">
         <is>
           <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>1号屋</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>7079</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2号屋</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>4706</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>268000000</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>56949</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>3号屋</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>4662</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>5号屋</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>4666</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>246580000</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>52846</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>6号屋</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>4737</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>7号屋</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>4728</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>8号屋</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>6723</v>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>9号屋</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>3601</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>10号屋</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>5239</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>322700000</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>61596</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>11号屋</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>3336</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>12号屋</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>2716</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>15号屋</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>2695</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>16号屋</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>3075</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>116800000</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>37984</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>17号屋</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>3059</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>18号屋</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>5509</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>362500000</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>65801</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>19号屋</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>3059</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>20号屋</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>3436</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>40163</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>21号屋</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>3297</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>138700000</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>42069</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>22号屋</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>3285</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>42009</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>23号屋</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>3272</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>139988888</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>42784</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>25号屋</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>3289</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>162820000</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>49504</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>26号屋</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>3350</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>27号屋</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>3304</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>146036800</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>44200</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>28号屋</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>5260</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>260341664</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>49495</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>29号屋</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>3382</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>30号屋</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>2738</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>107460000</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>39248</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>31号屋</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>2739</v>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-28</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>96136000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>35099</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>32号屋</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>3063</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>33号屋</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>3102</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>115238700</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>37150</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>35号屋</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>3102</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>115840200</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>37344</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>36号屋</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>3063</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>38号屋</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>4692</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>256000000</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>54561</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3066,1866 +4449,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 7座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 1170呎 (3房)
-$4,380万
-$37,440/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (3房)
-$4,380万
-$37,404/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 2511呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 1100呎 (3房)
-$2,911万
-$26,464/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1097呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 8座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 1170呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 1215呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 2456呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 2565呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 1100呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1097呎 (3房)
-$2,768万
-$25,232/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 9座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2&amp;3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 2452呎 (4+房)
-$8,776万
-$35,791/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 2437呎 (4+房)
-$8,223万
-$33,743/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;1/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 2436呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 2436呎 (4+房)
-$8,778万
-$36,034/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 10座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2&amp;3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 2452呎 (4+房)
-$8,620万
-$35,155/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 2551呎 (4+房)
-$8,307万
-$32,564/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;1/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 2466呎 (4+房)
-$17,361万
-$70,403/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 2466呎 (4+房)
-$17,361万
-$70,403/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 11座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2&amp;3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 2566呎 (4+房)
-$9,469万
-$36,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 2437呎 (4+房)
-$8,502万
-$34,887/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;1/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 2466呎 (4+房)
-$8,412万
-$34,111/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 2436呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr"/>
-      <c r="E7" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 12座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2&amp;3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 3212呎 (4+房)
-$11,980万
-$37,298/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;1/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 3198呎 (4+房)
-$12,776万
-$39,950/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2&amp;3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 1931呎 (4+房)
-$6,373万
-$33,002/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 1851呎 (4+房)
-$7,337万
-$39,638/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;1/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 1826呎 (4+房)
-$5,387万
-$29,502/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 1805呎 (4+房)
-$5,315万
-$29,446/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2&amp;3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 1931呎 (4+房)
-$6,083万
-$31,502/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 1851呎 (4+房)
-$6,109万
-$33,003/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;1/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 1826呎 (4+房)
-$5,254万
-$28,773/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 1805呎 (4+房)
-$5,533万
-$30,654/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 1871呎 (4+房)
-$6,752万
-$36,086/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 1874呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1855呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 844呎 (2房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 834呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr"/>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 1871呎 (4+房)
-$7,708万
-$41,197/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 1931呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 1910呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 844呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 834呎 (2房)
-$2,450万
-$29,376/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>One Stanley - 6座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 1170呎 (3房)
-$4,380万
-$37,440/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (3房)
-$4,382万
-$37,421/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 2511呎 (4+房)
-$6,812万
-$27,129/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>G/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 1100呎 (3房)
-$2,860万
-$26,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 1097呎 (3房)
-$3,159万
-$28,801/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-赤柱-One stanley.xlsx
+++ b/files/港岛-赤柱-One stanley.xlsx
@@ -8,6 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +52,132 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +188,48 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +275,81 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +726,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4449,4 +4701,2208 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>8座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 1170呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 1215呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 2456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 2565呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 1100呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1097呎 (3房)
+$2768万
+$25,232/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>9座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 2452呎 (4+房)
+$8776万
+$35,791/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 2437呎 (4+房)
+$8223万
+$33,743/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2436呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2436呎 (4+房)
+$8778万
+$36,034/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>One Stanley - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>34 套</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>5 套</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>19 套</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>9 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>位置 1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>位置 2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>位置 3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>位置 4</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>位置 5</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>位置 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>第 1 行</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>1号屋
+7079呎 (3房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>2号屋
+4706呎 (4+房)
+(26年-07月)
+$2.68亿
+$56,949/呎</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>3号屋
+4662呎 (4+房)
+(暂停销售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>5号屋
+4666呎 (4+房)
+(26年-02月)
+$2.47亿
+$52,846/呎</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>6号屋
+4737呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>7号屋
+4728呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>第 2 行</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>8号屋
+6723呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>9号屋
+3601呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>10号屋
+5239呎 (4+房)
+(25年-12月)
+$3.23亿
+$61,596/呎</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>11号屋
+3336呎 (4+房)
+(在售)
+招标项目
+-</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>12号屋
+2716呎 (4+房)
+(在售)
+招标项目
+-</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>12座
+3212呎 (4+房)
+(26年-06月)
+$1.20亿
+$37,298/呎</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>第 3 行</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>12座
+3198呎 (4+房)
+(26年-05月)
+$1.28亿
+$39,950/呎</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>15号屋
+2695呎 (4+房)
+(在售)
+招标项目
+-</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>16号屋
+3075呎 (4+房)
+(26年-06月)
+$1.17亿
+$37,984/呎</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>17号屋
+3059呎 (4+房)
+(在售)
+招标项目
+-</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>18号屋
+5509呎 (4+房)
+(25年-12月)
+$3.62亿
+$65,801/呎</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>19号屋
+3059呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>第 4 行</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>20号屋
+3436呎 (4+房)
+(25年-07月)
+$1.38亿
+$40,163/呎</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>21号屋
+3297呎 (4+房)
+(26年-04月)
+$1.39亿
+$42,069/呎</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>22号屋
+3285呎 (4+房)
+(25年-10月)
+$1.38亿
+$42,009/呎</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>23号屋
+3272呎 (4+房)
+(25年-09月)
+$1.40亿
+$42,784/呎</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>25号屋
+3289呎 (4+房)
+(26年-06月)
+$1.63亿
+$49,504/呎</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>26号屋
+3350呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>27号屋
+3304呎 (4+房)
+(24年-06月)
+$1.46亿
+$44,200/呎</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>28号屋
+5260呎 (4+房)
+(25年-04月)
+$2.60亿
+$49,495/呎</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>29号屋
+3382呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>30号屋
+2738呎 (4+房)
+(26年-02月)
+$1.07亿
+$39,248/呎</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>31号屋
+2739呎 (4+房)
+(24年-11月)
+$9,614万
+$35,099/呎</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>32号屋
+3063呎 (4+房)
+(在售)
+招标项目
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>33号屋
+3102呎 (4+房)
+(24年-05月)
+$1.15亿
+$37,150/呎</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>35号屋
+3102呎 (4+房)
+(24年-05月)
+$1.16亿
+$37,344/呎</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>36号屋
+3063呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>38号屋
+4692呎 (4+房)
+(25年-11月)
+$2.56亿
+$54,561/呎</t>
+        </is>
+      </c>
+      <c r="F11" s="30" t="inlineStr"/>
+      <c r="G11" s="30" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>10座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 2452呎 (4+房)
+$8620万
+$35,155/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 2551呎 (4+房)
+$8307万
+$32,564/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2466呎 (4+房)
+$17361万
+$70,403/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2466呎 (4+房)
+$17361万
+$70,403/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>11座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 2566呎 (4+房)
+$9469万
+$36,900/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 2437呎 (4+房)
+$8502万
+$34,887/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2466呎 (4+房)
+$8412万
+$34,111/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 2436呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1931呎 (4+房)
+$6373万
+$33,002/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1851呎 (4+房)
+$7337万
+$39,638/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 1826呎 (4+房)
+$5387万
+$29,502/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1805呎 (4+房)
+$5315万
+$29,446/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>2&amp;3</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1931呎 (4+房)
+$6083万
+$31,502/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1851呎 (4+房)
+$6109万
+$33,003/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>G&amp;1</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 1826呎 (4+房)
+$5254万
+$28,773/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1805呎 (4+房)
+$5533万
+$30,654/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1871呎 (4+房)
+$6752万
+$36,086/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1874呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1855呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>A | 844呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 834呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1871呎 (4+房)
+$7708万
+$41,197/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 1931呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 1910呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 844呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 834呎 (2房)
+$2450万
+$29,376/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1170呎 (3房)
+$4380万
+$37,440/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (3房)
+$4382万
+$37,421/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2511呎 (4+房)
+$6812万
+$27,129/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1100呎 (3房)
+$2860万
+$26,000/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 1097呎 (3房)
+$3159万
+$28,801/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>7座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1170呎 (3房)
+$4380万
+$37,440/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (3房)
+$4380万
+$37,404/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 2511呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1100呎 (3房)
+$2911万
+$26,464/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1097呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-赤柱-One stanley.xlsx
+++ b/files/港岛-赤柱-One stanley.xlsx
@@ -726,7 +726,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-赤柱-One stanley.xlsx
+++ b/files/港岛-赤柱-One stanley.xlsx
@@ -716,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -729,6 +729,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -786,6 +790,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -832,6 +856,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -878,6 +922,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -924,6 +988,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -970,6 +1054,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1016,6 +1120,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1062,6 +1186,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1112,6 +1256,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1158,6 +1322,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1204,6 +1388,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1250,6 +1454,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1296,6 +1520,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1342,6 +1586,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1388,6 +1652,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1434,6 +1718,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1480,6 +1784,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1526,6 +1850,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1572,6 +1916,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1618,6 +1982,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1664,6 +2048,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1714,6 +2118,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1764,6 +2188,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1814,6 +2258,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1864,6 +2328,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1910,6 +2394,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1960,6 +2464,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2010,6 +2534,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2056,6 +2600,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2106,6 +2670,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2152,6 +2736,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2198,6 +2802,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2244,6 +2868,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2294,6 +2938,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2340,6 +3004,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2386,6 +3070,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2432,6 +3136,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2478,6 +3202,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2528,6 +3272,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2578,6 +3342,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2628,6 +3412,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2674,6 +3478,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2724,6 +3548,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2774,6 +3618,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2824,6 +3688,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2874,6 +3758,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2920,6 +3824,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2970,6 +3894,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3016,6 +3960,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3062,6 +4026,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3108,6 +4092,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3158,6 +4162,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3208,6 +4232,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3254,6 +4298,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3304,6 +4368,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3350,6 +4434,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3400,6 +4504,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3450,6 +4574,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3500,6 +4644,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3550,6 +4714,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3596,6 +4780,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3646,6 +4850,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3696,6 +4920,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3746,6 +4990,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3772,7 +5036,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>3075</v>
+        <v>3053</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -3781,16 +5045,36 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
         <v>116800000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>37984</v>
+        <v>38257</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3842,6 +5126,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3888,6 +5192,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3938,6 +5262,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3984,6 +5328,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4030,6 +5394,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4076,6 +5460,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4122,6 +5526,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4168,6 +5592,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4218,6 +5662,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4264,6 +5728,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4310,6 +5794,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4360,6 +5864,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4406,6 +5930,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4452,6 +5996,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4502,6 +6066,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4548,6 +6132,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4594,6 +6198,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4644,6 +6268,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4690,13 +6334,33 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4870,7 +6534,7 @@
           <t>B | 1097呎 (3房)
 $2768万
 $25,232/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
     </row>
@@ -5010,7 +6674,7 @@
           <t>C | 2452呎 (4+房)
 $8776万
 $35,791/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -5018,7 +6682,7 @@
           <t>D | 2437呎 (4+房)
 $8223万
 $33,743/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
     </row>
@@ -5041,7 +6705,7 @@
           <t>B | 2436呎 (4+房)
 $8778万
 $36,034/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5201,7 +6865,7 @@
         <is>
           <t>2号屋
 4706呎 (4+房)
-(26年-07月)
+(26年-07月-06日)
 $2.68亿
 $56,949/呎</t>
         </is>
@@ -5219,7 +6883,7 @@
         <is>
           <t>5号屋
 4666呎 (4+房)
-(26年-02月)
+(26年-02月-09日)
 $2.47亿
 $52,846/呎</t>
         </is>
@@ -5271,7 +6935,7 @@
         <is>
           <t>10号屋
 5239呎 (4+房)
-(25年-12月)
+(25年-12月-23日)
 $3.23亿
 $61,596/呎</t>
         </is>
@@ -5298,7 +6962,7 @@
         <is>
           <t>12座
 3212呎 (4+房)
-(26年-06月)
+(26年-06月-07日)
 $1.20亿
 $37,298/呎</t>
         </is>
@@ -5314,7 +6978,7 @@
         <is>
           <t>12座
 3198呎 (4+房)
-(26年-05月)
+(26年-05月-18日)
 $1.28亿
 $39,950/呎</t>
         </is>
@@ -5331,10 +6995,10 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t>16号屋
-3075呎 (4+房)
-(26年-06月)
+3053呎 (4+房)
+(26年-07月-12日)
 $1.17亿
-$37,984/呎</t>
+$38,257/呎</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -5350,7 +7014,7 @@
         <is>
           <t>18号屋
 5509呎 (4+房)
-(25年-12月)
+(25年-12月-23日)
 $3.62亿
 $65,801/呎</t>
         </is>
@@ -5375,7 +7039,7 @@
         <is>
           <t>20号屋
 3436呎 (4+房)
-(25年-07月)
+(25年-07月-22日)
 $1.38亿
 $40,163/呎</t>
         </is>
@@ -5384,7 +7048,7 @@
         <is>
           <t>21号屋
 3297呎 (4+房)
-(26年-04月)
+(26年-04月-22日)
 $1.39亿
 $42,069/呎</t>
         </is>
@@ -5393,7 +7057,7 @@
         <is>
           <t>22号屋
 3285呎 (4+房)
-(25年-10月)
+(25年-10月-05日)
 $1.38亿
 $42,009/呎</t>
         </is>
@@ -5402,7 +7066,7 @@
         <is>
           <t>23号屋
 3272呎 (4+房)
-(25年-09月)
+(25年-09月-03日)
 $1.40亿
 $42,784/呎</t>
         </is>
@@ -5411,7 +7075,7 @@
         <is>
           <t>25号屋
 3289呎 (4+房)
-(26年-06月)
+(26年-06月-25日)
 $1.63亿
 $49,504/呎</t>
         </is>
@@ -5436,7 +7100,7 @@
         <is>
           <t>27号屋
 3304呎 (4+房)
-(24年-06月)
+(24年-06月-24日)
 $1.46亿
 $44,200/呎</t>
         </is>
@@ -5445,7 +7109,7 @@
         <is>
           <t>28号屋
 5260呎 (4+房)
-(25年-04月)
+(25年-04月-07日)
 $2.60亿
 $49,495/呎</t>
         </is>
@@ -5463,7 +7127,7 @@
         <is>
           <t>30号屋
 2738呎 (4+房)
-(26年-02月)
+(26年-02月-12日)
 $1.07亿
 $39,248/呎</t>
         </is>
@@ -5472,7 +7136,7 @@
         <is>
           <t>31号屋
 2739呎 (4+房)
-(24年-11月)
+(24年-11月-28日)
 $9,614万
 $35,099/呎</t>
         </is>
@@ -5497,7 +7161,7 @@
         <is>
           <t>33号屋
 3102呎 (4+房)
-(24年-05月)
+(24年-05月-29日)
 $1.15亿
 $37,150/呎</t>
         </is>
@@ -5506,7 +7170,7 @@
         <is>
           <t>35号屋
 3102呎 (4+房)
-(24年-05月)
+(24年-05月-13日)
 $1.16亿
 $37,344/呎</t>
         </is>
@@ -5524,7 +7188,7 @@
         <is>
           <t>38号屋
 4692呎 (4+房)
-(25年-11月)
+(25年-11月-06日)
 $2.56亿
 $54,561/呎</t>
         </is>
@@ -5668,7 +7332,7 @@
           <t>C | 2452呎 (4+房)
 $8620万
 $35,155/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -5676,7 +7340,7 @@
           <t>D | 2551呎 (4+房)
 $8307万
 $32,564/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -5691,7 +7355,7 @@
           <t>A | 2466呎 (4+房)
 $17361万
 $70,403/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -5699,7 +7363,7 @@
           <t>B | 2466呎 (4+房)
 $17361万
 $70,403/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5841,7 +7505,7 @@
           <t>C | 2566呎 (4+房)
 $9469万
 $36,900/呎
-(24年-08月)</t>
+(24年-08月-04日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -5849,7 +7513,7 @@
           <t>D | 2437呎 (4+房)
 $8502万
 $34,887/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -5864,7 +7528,7 @@
           <t>A | 2466呎 (4+房)
 $8412万
 $34,111/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -6000,7 +7664,7 @@
           <t>A | 1931呎 (4+房)
 $6373万
 $33,002/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -6008,7 +7672,7 @@
           <t>B | 1851呎 (4+房)
 $7337万
 $39,638/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -6023,7 +7687,7 @@
           <t>A | 1826呎 (4+房)
 $5387万
 $29,502/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -6031,7 +7695,7 @@
           <t>B | 1805呎 (4+房)
 $5315万
 $29,446/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -6157,7 +7821,7 @@
           <t>A | 1931呎 (4+房)
 $6083万
 $31,502/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -6165,7 +7829,7 @@
           <t>B | 1851呎 (4+房)
 $6109万
 $33,003/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -6180,7 +7844,7 @@
           <t>A | 1826呎 (4+房)
 $5254万
 $28,773/呎
-(25年-02月)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -6188,7 +7852,7 @@
           <t>B | 1805呎 (4+房)
 $5533万
 $30,654/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -6314,7 +7978,7 @@
           <t>A | 1871呎 (4+房)
 $6752万
 $36,086/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr"/>
@@ -6488,7 +8152,7 @@
           <t>B | 1871呎 (4+房)
 $7708万
 $41,197/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -6534,7 +8198,7 @@
           <t>B | 834呎 (2房)
 $2450万
 $29,376/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -6660,7 +8324,7 @@
           <t>A | 1170呎 (3房)
 $4380万
 $37,440/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -6668,7 +8332,7 @@
           <t>B | 1171呎 (3房)
 $4382万
 $37,421/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -6691,7 +8355,7 @@
           <t>B | 2511呎 (4+房)
 $6812万
 $27,129/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -6706,7 +8370,7 @@
           <t>A | 1100呎 (3房)
 $2860万
 $26,000/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -6714,7 +8378,7 @@
           <t>B | 1097呎 (3房)
 $3159万
 $28,801/呎
-(25年-03月)</t>
+(25年-03月-05日)</t>
         </is>
       </c>
     </row>
@@ -6840,7 +8504,7 @@
           <t>A | 1170呎 (3房)
 $4380万
 $37,440/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -6848,7 +8512,7 @@
           <t>B | 1171呎 (3房)
 $4380万
 $37,404/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -6886,7 +8550,7 @@
           <t>A | 1100呎 (3房)
 $2911万
 $26,464/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">

--- a/files/港岛-赤柱-One stanley.xlsx
+++ b/files/港岛-赤柱-One stanley.xlsx
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -176,6 +176,11 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -259,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -347,6 +352,9 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4348,7 +4356,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4358,12 +4366,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -4373,12 +4381,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4388,7 +4396,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6256,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6258,12 +6266,12 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -6273,12 +6281,12 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -6288,7 +6296,7 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6790,22 +6798,22 @@
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>19 套</t>
+        </is>
+      </c>
+      <c r="E3" s="29" t="inlineStr">
+        <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
-        <is>
-          <t>19 套</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>9 套</t>
+          <t>8 套</t>
         </is>
       </c>
     </row>
@@ -6870,13 +6878,13 @@
 $56,949/呎</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>3号屋
 4662呎 (4+房)
-(暂停销售)
-暂无价格
-暂无呎价</t>
+(已定价未售)
+招标单位
+-</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -7175,13 +7183,13 @@
 $37,344/呎</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>36号屋
 3063呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
+(已定价未售)
+招标单位
+-</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -7193,8 +7201,8 @@
 $54,561/呎</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr"/>
-      <c r="G11" s="30" t="inlineStr"/>
+      <c r="F11" s="31" t="inlineStr"/>
+      <c r="G11" s="31" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/files/港岛-赤柱-One stanley.xlsx
+++ b/files/港岛-赤柱-One stanley.xlsx
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4197,7 +4197,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>1号屋</t>
+          <t>2号屋</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4212,31 +4212,27 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>7079</v>
+        <v>4706</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>268000000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>56949</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4267,7 +4263,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2号屋</t>
+          <t>3号屋</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -4286,23 +4282,27 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>4706</v>
+        <v>4662</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>268000000</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>56949</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4311,12 +4311,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4326,14 +4326,14 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3号屋</t>
+          <t>5号屋</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4352,27 +4352,23 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4662</v>
+        <v>4666</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>246580000</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>52846</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4381,12 +4377,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4396,14 +4392,14 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>5号屋</t>
+          <t>6号屋</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4422,23 +4418,27 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>4666</v>
+        <v>4737</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>246580000</v>
-      </c>
-      <c r="I56" s="5" t="n">
-        <v>52846</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6号屋</t>
+          <t>7号屋</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>4737</v>
+        <v>4728</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>7号屋</t>
+          <t>8号屋</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>4728</v>
+        <v>6723</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>8号屋</t>
+          <t>9号屋</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>6723</v>
+        <v>3601</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>9号屋</t>
+          <t>10号屋</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -4698,27 +4698,23 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>3601</v>
+        <v>5239</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>322700000</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>61596</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4749,7 +4745,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>10号屋</t>
+          <t>11号屋</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4768,7 +4764,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5239</v>
+        <v>3336</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4777,14 +4773,14 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>322700000</v>
+        <v>151080000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>61596</v>
+        <v>45288</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4815,7 +4811,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>12号屋</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4834,7 +4830,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>3336</v>
+        <v>2716</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4885,7 +4881,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>15号屋</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4904,7 +4900,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2716</v>
+        <v>2695</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4955,7 +4951,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>15号屋</t>
+          <t>16号屋</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4974,27 +4970,23 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2695</v>
+        <v>3053</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>116800000</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>38257</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -5003,12 +4995,12 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -5018,14 +5010,14 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>16号屋</t>
+          <t>17号屋</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -5044,23 +5036,27 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>3053</v>
+        <v>3059</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>116800000</v>
-      </c>
-      <c r="I65" s="5" t="n">
-        <v>38257</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -5069,12 +5065,12 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -5084,14 +5080,14 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>17号屋</t>
+          <t>18号屋</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -5110,27 +5106,23 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>3059</v>
+        <v>5509</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>362500000</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>65801</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5139,12 +5131,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -5154,14 +5146,14 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>18号屋</t>
+          <t>19号屋</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5180,23 +5172,27 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>5509</v>
+        <v>3059</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="n">
-        <v>362500000</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>65801</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5227,7 +5223,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>19号屋</t>
+          <t>20号屋</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -5246,27 +5242,23 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>3059</v>
+        <v>3436</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>40163</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5297,7 +5289,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>20号屋</t>
+          <t>21号屋</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5316,7 +5308,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>3436</v>
+        <v>3297</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -5325,14 +5317,14 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>138000000</v>
+        <v>138700000</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>40163</v>
+        <v>42069</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -5363,7 +5355,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>21号屋</t>
+          <t>22号屋</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -5382,7 +5374,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>3297</v>
+        <v>3285</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -5391,14 +5383,14 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>138700000</v>
+        <v>138000000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>42069</v>
+        <v>42009</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -5429,7 +5421,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>22号屋</t>
+          <t>23号屋</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -5448,7 +5440,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>3285</v>
+        <v>3272</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5457,14 +5449,14 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>138000000</v>
+        <v>139988888</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>42009</v>
+        <v>42784</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5495,7 +5487,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>23号屋</t>
+          <t>25号屋</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -5514,7 +5506,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>3272</v>
+        <v>3289</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5523,14 +5515,14 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>139988888</v>
+        <v>162820000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>42784</v>
+        <v>49504</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5561,7 +5553,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>25号屋</t>
+          <t>26号屋</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5580,23 +5572,27 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>3289</v>
+        <v>3350</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>162820000</v>
-      </c>
-      <c r="I73" s="5" t="n">
-        <v>49504</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5627,7 +5623,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26号屋</t>
+          <t>27号屋</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5646,27 +5642,23 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>3350</v>
+        <v>3304</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>146036800</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>44200</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5697,7 +5689,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>27号屋</t>
+          <t>28号屋</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5716,7 +5708,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>3304</v>
+        <v>5260</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5725,14 +5717,14 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>146036800</v>
+        <v>260341664</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>44200</v>
+        <v>49495</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5763,7 +5755,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>28号屋</t>
+          <t>29号屋</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5782,23 +5774,27 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>5260</v>
+        <v>3382</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>260341664</v>
-      </c>
-      <c r="I76" s="5" t="n">
-        <v>49495</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5829,7 +5825,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>29号屋</t>
+          <t>30号屋</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5848,27 +5844,23 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>3382</v>
+        <v>2738</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>107460000</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>39248</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5899,7 +5891,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>30号屋</t>
+          <t>31号屋</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -5918,7 +5910,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5927,14 +5919,14 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>107460000</v>
+        <v>96136000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>39248</v>
+        <v>35099</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5965,7 +5957,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>31号屋</t>
+          <t>32号屋</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5984,23 +5976,27 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>2739</v>
+        <v>3063</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>96136000</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>35099</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -6009,12 +6005,12 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -6024,14 +6020,14 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>32号屋</t>
+          <t>33号屋</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -6050,27 +6046,23 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>3063</v>
+        <v>3102</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>115238700</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>37150</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6079,12 +6071,12 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -6094,14 +6086,14 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>33号屋</t>
+          <t>35号屋</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -6129,14 +6121,14 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>115238700</v>
+        <v>115840200</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>37150</v>
+        <v>37344</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6167,7 +6159,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>35号屋</t>
+          <t>36号屋</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -6186,23 +6178,27 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>3102</v>
+        <v>3063</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="n">
-        <v>115840200</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>37344</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6211,12 +6207,12 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -6226,14 +6222,14 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>36号屋</t>
+          <t>38号屋</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -6252,27 +6248,23 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>3063</v>
+        <v>4692</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>256000000</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>54561</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6281,12 +6273,12 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -6295,72 +6287,6 @@
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>38号屋</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>4692</v>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="n">
-        <v>256000000</v>
-      </c>
-      <c r="I84" s="5" t="n">
-        <v>54561</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N84" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6542,7 +6468,7 @@
           <t>B | 1097呎 (3房)
 $2768万
 $25,232/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6608,7 @@
           <t>C | 2452呎 (4+房)
 $8776万
 $35,791/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -6690,7 +6616,7 @@
           <t>D | 2437呎 (4+房)
 $8223万
 $33,743/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6639,7 @@
           <t>B | 2436呎 (4+房)
 $8778万
 $36,034/呎
-(25年-10月-30日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -6788,12 +6714,12 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>34 套</t>
+          <t>33 套</t>
         </is>
       </c>
       <c r="B3" s="26" t="inlineStr">
         <is>
-          <t>5 套</t>
+          <t>4 套</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
@@ -6803,7 +6729,7 @@
       </c>
       <c r="D3" s="28" t="inlineStr">
         <is>
-          <t>19 套</t>
+          <t>20 套</t>
         </is>
       </c>
       <c r="E3" s="29" t="inlineStr">
@@ -6813,7 +6739,7 @@
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>8 套</t>
+          <t>7 套</t>
         </is>
       </c>
     </row>
@@ -6860,25 +6786,16 @@
           <t>第 1 行</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>1号屋
-7079呎 (3房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>2号屋
 4706呎 (4+房)
-(26年-07月-06日)
+(26年-07月)
 $2.68亿
 $56,949/呎</t>
         </is>
       </c>
-      <c r="D6" s="30" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>3号屋
 4662呎 (4+房)
@@ -6887,16 +6804,16 @@
 -</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>5号屋
 4666呎 (4+房)
-(26年-02月-09日)
+(26年-02月)
 $2.47亿
 $52,846/呎</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>6号屋
 4737呎 (4+房)
@@ -6905,7 +6822,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>7号屋
 4728呎 (4+房)
@@ -6914,14 +6831,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>第 2 行</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>8号屋
 6723呎 (4+房)
@@ -6930,7 +6840,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>第 2 行</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>9号屋
 3601呎 (4+房)
@@ -6939,25 +6856,25 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>10号屋
 5239呎 (4+房)
-(25年-12月-23日)
+(25年-12月)
 $3.23亿
 $61,596/呎</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>11号屋
 3336呎 (4+房)
-(在售)
-招标项目
--</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
+(26年-07月)
+$1.51亿
+$45,288/呎</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>12号屋
 2716呎 (4+房)
@@ -6966,15 +6883,24 @@
 -</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>12座
 3212呎 (4+房)
-(26年-06月-07日)
+(26年-06月)
 $1.20亿
 $37,298/呎</t>
         </is>
       </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>12座
+3198呎 (4+房)
+(26年-05月)
+$1.28亿
+$39,950/呎</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -6982,16 +6908,7 @@
           <t>第 3 行</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>12座
-3198呎 (4+房)
-(26年-05月-18日)
-$1.28亿
-$39,950/呎</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>15号屋
 2695呎 (4+房)
@@ -7000,16 +6917,16 @@
 -</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>16号屋
 3053呎 (4+房)
-(26年-07月-12日)
+(26年-07月)
 $1.17亿
 $38,257/呎</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>17号屋
 3059呎 (4+房)
@@ -7018,16 +6935,16 @@
 -</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>18号屋
 5509呎 (4+房)
-(25年-12月-23日)
+(25年-12月)
 $3.62亿
 $65,801/呎</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>19号屋
 3059呎 (4+房)
@@ -7036,6 +6953,15 @@
 暂无呎价</t>
         </is>
       </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>20号屋
+3436呎 (4+房)
+(25年-07月)
+$1.38亿
+$40,163/呎</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -7045,50 +6971,41 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>20号屋
-3436呎 (4+房)
-(25年-07月-22日)
-$1.38亿
-$40,163/呎</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
           <t>21号屋
 3297呎 (4+房)
-(26年-04月-22日)
+(26年-04月)
 $1.39亿
 $42,069/呎</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>22号屋
 3285呎 (4+房)
-(25年-10月-05日)
+(25年-10月)
 $1.38亿
 $42,009/呎</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>23号屋
 3272呎 (4+房)
-(25年-09月-03日)
+(25年-09月)
 $1.40亿
 $42,784/呎</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>25号屋
 3289呎 (4+房)
-(26年-06月-25日)
+(26年-06月)
 $1.63亿
 $49,504/呎</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>26号屋
 3350呎 (4+房)
@@ -7097,6 +7014,15 @@
 暂无呎价</t>
         </is>
       </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>27号屋
+3304呎 (4+房)
+(24年-06月)
+$1.46亿
+$44,200/呎</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -7106,23 +7032,14 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>27号屋
-3304呎 (4+房)
-(24年-06月-24日)
-$1.46亿
-$44,200/呎</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
           <t>28号屋
 5260呎 (4+房)
-(25年-04月-07日)
+(25年-04月)
 $2.60亿
 $49,495/呎</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>29号屋
 3382呎 (4+房)
@@ -7131,25 +7048,25 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>30号屋
 2738呎 (4+房)
-(26年-02月-12日)
+(26年-02月)
 $1.07亿
 $39,248/呎</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>31号屋
 2739呎 (4+房)
-(24年-11月-28日)
+(24年-11月)
 $9,614万
 $35,099/呎</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>32号屋
 3063呎 (4+房)
@@ -7158,6 +7075,15 @@
 -</t>
         </is>
       </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>33号屋
+3102呎 (4+房)
+(24年-05月)
+$1.15亿
+$37,150/呎</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="80" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -7167,23 +7093,14 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>33号屋
-3102呎 (4+房)
-(24年-05月-29日)
-$1.15亿
-$37,150/呎</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
           <t>35号屋
 3102呎 (4+房)
-(24年-05月-13日)
+(24年-05月)
 $1.16亿
 $37,344/呎</t>
         </is>
       </c>
-      <c r="D11" s="30" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>36号屋
 3063呎 (4+房)
@@ -7192,15 +7109,16 @@
 -</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>38号屋
 4692呎 (4+房)
-(25年-11月-06日)
+(25年-11月)
 $2.56亿
 $54,561/呎</t>
         </is>
       </c>
+      <c r="E11" s="31" t="inlineStr"/>
       <c r="F11" s="31" t="inlineStr"/>
       <c r="G11" s="31" t="inlineStr"/>
     </row>
@@ -7340,7 +7258,7 @@
           <t>C | 2452呎 (4+房)
 $8620万
 $35,155/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -7348,7 +7266,7 @@
           <t>D | 2551呎 (4+房)
 $8307万
 $32,564/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7281,7 @@
           <t>A | 2466呎 (4+房)
 $17361万
 $70,403/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -7371,7 +7289,7 @@
           <t>B | 2466呎 (4+房)
 $17361万
 $70,403/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -7513,7 +7431,7 @@
           <t>C | 2566呎 (4+房)
 $9469万
 $36,900/呎
-(24年-08月-04日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -7521,7 +7439,7 @@
           <t>D | 2437呎 (4+房)
 $8502万
 $34,887/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7454,7 @@
           <t>A | 2466呎 (4+房)
 $8412万
 $34,111/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -7672,7 +7590,7 @@
           <t>A | 1931呎 (4+房)
 $6373万
 $33,002/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -7680,7 +7598,7 @@
           <t>B | 1851呎 (4+房)
 $7337万
 $39,638/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7613,7 @@
           <t>A | 1826呎 (4+房)
 $5387万
 $29,502/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -7703,7 +7621,7 @@
           <t>B | 1805呎 (4+房)
 $5315万
 $29,446/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7747,7 @@
           <t>A | 1931呎 (4+房)
 $6083万
 $31,502/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -7837,7 +7755,7 @@
           <t>B | 1851呎 (4+房)
 $6109万
 $33,003/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7770,7 @@
           <t>A | 1826呎 (4+房)
 $5254万
 $28,773/呎
-(25年-02月-05日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -7860,7 +7778,7 @@
           <t>B | 1805呎 (4+房)
 $5533万
 $30,654/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7904,7 @@
           <t>A | 1871呎 (4+房)
 $6752万
 $36,086/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr"/>
@@ -8160,7 +8078,7 @@
           <t>B | 1871呎 (4+房)
 $7708万
 $41,197/呎
-(25年-02月-17日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8124,7 @@
           <t>B | 834呎 (2房)
 $2450万
 $29,376/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8250,7 @@
           <t>A | 1170呎 (3房)
 $4380万
 $37,440/呎
-(25年-07月-21日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -8340,7 +8258,7 @@
           <t>B | 1171呎 (3房)
 $4382万
 $37,421/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -8363,7 +8281,7 @@
           <t>B | 2511呎 (4+房)
 $6812万
 $27,129/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8296,7 @@
           <t>A | 1100呎 (3房)
 $2860万
 $26,000/呎
-(25年-04月-22日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -8386,7 +8304,7 @@
           <t>B | 1097呎 (3房)
 $3159万
 $28,801/呎
-(25年-03月-05日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -8512,7 +8430,7 @@
           <t>A | 1170呎 (3房)
 $4380万
 $37,440/呎
-(25年-03月-10日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -8520,7 +8438,7 @@
           <t>B | 1171呎 (3房)
 $4380万
 $37,404/呎
-(25年-05月-14日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8476,7 @@
           <t>A | 1100呎 (3房)
 $2911万
 $26,464/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">

--- a/files/港岛-赤柱-One stanley.xlsx
+++ b/files/港岛-赤柱-One stanley.xlsx
@@ -9,16 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9座" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -131,13 +130,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -329,10 +328,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -724,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1089,7 +1088,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>11座</t>
+          <t>12座</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1099,7 +1098,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1108,7 +1107,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2437</v>
+        <v>3212</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1117,14 +1116,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>85020000</v>
+        <v>119800000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>34887</v>
+        <v>37298</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1155,17 +1154,17 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>11座</t>
+          <t>12座</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2&amp;3</t>
+          <t>G&amp;1</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1174,7 +1173,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2566</v>
+        <v>3198</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1183,14 +1182,14 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>94685400</v>
+        <v>127760000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>36900</v>
+        <v>39950</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1221,12 +1220,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>11座</t>
+          <t>1座</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
+          <t>2&amp;3</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1240,27 +1239,23 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2436</v>
+        <v>1851</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>73370000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>39638</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1269,12 +1264,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1284,19 +1279,19 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>11座</t>
+          <t>1座</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
+          <t>2&amp;3</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1310,7 +1305,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2466</v>
+        <v>1931</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1319,14 +1314,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>84118889</v>
+        <v>63727200</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>34111</v>
+        <v>33002</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1357,12 +1352,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>12座</t>
+          <t>1座</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2&amp;3</t>
+          <t>G&amp;1</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1376,7 +1371,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3212</v>
+        <v>1805</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1385,14 +1380,14 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>119800000</v>
+        <v>53150350</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>37298</v>
+        <v>29446</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1423,7 +1418,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>12座</t>
+          <t>1座</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1442,7 +1437,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3198</v>
+        <v>1826</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1451,14 +1446,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>127760000</v>
+        <v>53870000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>39950</v>
+        <v>29502</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1489,7 +1484,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>1座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1517,14 +1512,14 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>73370000</v>
+        <v>61088000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>39638</v>
+        <v>33003</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1555,7 +1550,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>1座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1583,14 +1578,14 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>63727200</v>
+        <v>60830700</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>33002</v>
+        <v>31502</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1621,7 +1616,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>1座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1649,14 +1644,14 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>53150350</v>
+        <v>55330000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>29446</v>
+        <v>30654</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1687,7 +1682,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>1座</t>
+          <t>2座</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1715,14 +1710,14 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>53870000</v>
+        <v>52540000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>29502</v>
+        <v>28773</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1753,17 +1748,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2&amp;3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1772,7 +1767,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1851</v>
+        <v>1871</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1781,14 +1776,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>61088000</v>
+        <v>67516975</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>33003</v>
+        <v>36086</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1819,17 +1814,17 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2&amp;3</t>
+          <t>1&amp;2</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1838,23 +1833,27 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1931</v>
+        <v>1855</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>60830700</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>31502</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1863,12 +1862,12 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -1878,24 +1877,24 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
+          <t>1&amp;2</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1904,23 +1903,27 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1805</v>
+        <v>1874</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>55330000</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>30654</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1951,42 +1954,46 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2座</t>
+          <t>3座</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1826</v>
+        <v>834</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>52540000</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>28773</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2022,7 +2029,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2032,27 +2039,31 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1871</v>
+        <v>844</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>67516975</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>36086</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2083,12 +2094,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>1&amp;2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2102,27 +2113,23 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1855</v>
+        <v>1871</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>77078792</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>41197</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2131,12 +2138,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2146,14 +2153,14 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2163,7 +2170,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2172,7 +2179,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1874</v>
+        <v>1910</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2223,26 +2230,26 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>1&amp;2</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>834</v>
+        <v>1931</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2293,7 +2300,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3座</t>
+          <t>5座</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2303,7 +2310,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -2312,27 +2319,23 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>24500000</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>29376</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2368,37 +2371,41 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>2房</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1871</v>
+        <v>844</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>77078792</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>41197</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2407,12 +2414,12 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2422,19 +2429,19 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>1&amp;2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2444,31 +2451,27 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1910</v>
+        <v>1171</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>43820000</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>37421</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2499,12 +2502,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>1&amp;2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2514,31 +2517,27 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1931</v>
+        <v>1170</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>43804800</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>37440</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2569,12 +2568,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>1&amp;2</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2584,11 +2583,11 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>834</v>
+        <v>2511</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2597,14 +2596,14 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>24500000</v>
+        <v>68120000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>29376</v>
+        <v>27129</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2635,12 +2634,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>5座</t>
+          <t>6座</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>1&amp;2</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2650,15 +2649,15 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>2房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>844</v>
+        <v>2403</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2668,12 +2667,12 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2683,12 +2682,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2698,7 +2697,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2709,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2724,7 +2723,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1171</v>
+        <v>1097</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2733,14 +2732,14 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>43820000</v>
+        <v>31594600</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>37421</v>
+        <v>28801</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2776,7 +2775,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2790,7 +2789,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1170</v>
+        <v>1100</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2799,14 +2798,14 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>43804800</v>
+        <v>28600000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>37440</v>
+        <v>26000</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2837,12 +2836,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>7座</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>1&amp;2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2852,11 +2851,11 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2511</v>
+        <v>1171</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2865,14 +2864,14 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>68120000</v>
+        <v>43800000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>27129</v>
+        <v>37404</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2903,12 +2902,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>7座</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>1&amp;2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2918,31 +2917,27 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2403</v>
+        <v>1170</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>43804800</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>37440</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2973,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>7座</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>1&amp;2</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2988,27 +2983,31 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1097</v>
+        <v>2511</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>31594600</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>28801</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -3017,12 +3016,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3032,19 +3031,19 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6座</t>
+          <t>7座</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>1&amp;2</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -3054,27 +3053,31 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1100</v>
+        <v>2403</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>28600000</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>26000</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3110,7 +3113,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -3124,23 +3127,27 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1171</v>
+        <v>1097</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>43800000</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>37404</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3149,12 +3156,12 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
@@ -3164,7 +3171,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3183,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3190,7 +3197,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1170</v>
+        <v>1100</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3199,14 +3206,14 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>43804800</v>
+        <v>29110000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>37440</v>
+        <v>26464</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3237,12 +3244,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>7座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>1&amp;2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3252,11 +3259,11 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2511</v>
+        <v>1215</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3307,12 +3314,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>7座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>1&amp;2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -3322,15 +3329,15 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2403</v>
+        <v>1170</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -3340,12 +3347,12 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -3355,12 +3362,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -3370,19 +3377,19 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>7座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>1&amp;2</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -3392,15 +3399,15 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1097</v>
+        <v>2565</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3410,12 +3417,12 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -3425,12 +3432,12 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -3440,19 +3447,19 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7座</t>
+          <t>8座</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>1&amp;2</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3462,27 +3469,31 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1100</v>
+        <v>2456</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>29110000</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>26464</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3518,7 +3529,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3532,27 +3543,23 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1215</v>
+        <v>1097</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>27680000</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>25232</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3561,12 +3568,12 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -3576,7 +3583,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3595,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -3602,11 +3609,11 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1170</v>
+        <v>1100</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3616,12 +3623,12 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -3631,12 +3638,12 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -3646,24 +3653,24 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>9座</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>1&amp;2</t>
+          <t>2&amp;3</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3672,27 +3679,23 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2565</v>
+        <v>2437</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>82231500</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>33743</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3723,17 +3726,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>9座</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>1&amp;2</t>
+          <t>2&amp;3</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3742,27 +3745,23 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2456</v>
+        <v>2452</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>87760000</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>35791</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3793,12 +3792,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>9座</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G&amp;1</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3808,11 +3807,11 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1097</v>
+        <v>2436</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3821,14 +3820,14 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>27680000</v>
+        <v>87780000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>25232</v>
+        <v>36034</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3859,12 +3858,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8座</t>
+          <t>9座</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>G&amp;1</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3874,15 +3873,15 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1100</v>
+        <v>2436</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3892,12 +3891,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3907,12 +3906,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3922,49 +3921,53 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>9座</t>
+          <t>1号屋</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>2&amp;3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>2437</v>
+        <v>7079</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>82231500</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>33743</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3995,17 +3998,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9座</t>
+          <t>2号屋</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>2&amp;3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -4014,7 +4017,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>2452</v>
+        <v>4706</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -4023,14 +4026,14 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>87760000</v>
+        <v>268000000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>35791</v>
+        <v>56949</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -4061,17 +4064,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>9座</t>
+          <t>3号屋</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -4080,23 +4083,27 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2436</v>
+        <v>4662</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>87780000</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>36034</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4105,12 +4112,12 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -4120,24 +4127,24 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>9座</t>
+          <t>5号屋</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -4146,27 +4153,23 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2436</v>
+        <v>4666</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>246580000</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>52846</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4175,12 +4178,12 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -4190,14 +4193,14 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2号屋</t>
+          <t>6号屋</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4216,23 +4219,27 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>4706</v>
+        <v>4737</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>268000000</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>56949</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4263,7 +4270,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3号屋</t>
+          <t>7号屋</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -4282,11 +4289,11 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>4662</v>
+        <v>4728</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4296,12 +4303,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -4311,12 +4318,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4326,14 +4333,14 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>5号屋</t>
+          <t>8号屋</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4352,23 +4359,27 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>4666</v>
+        <v>6723</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>246580000</v>
-      </c>
-      <c r="I55" s="5" t="n">
-        <v>52846</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4399,7 +4410,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6号屋</t>
+          <t>9号屋</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4418,7 +4429,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>4737</v>
+        <v>3601</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4469,7 +4480,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>7号屋</t>
+          <t>10号屋</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4488,27 +4499,23 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>4728</v>
+        <v>5239</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>322700000</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>61596</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4539,7 +4546,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>8号屋</t>
+          <t>11号屋</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -4558,27 +4565,23 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>6723</v>
+        <v>3336</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>151080000</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>45288</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4609,7 +4612,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>9号屋</t>
+          <t>12号屋</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4628,11 +4631,11 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>3601</v>
+        <v>2716</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4642,12 +4645,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -4657,12 +4660,12 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4672,14 +4675,14 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>10号屋</t>
+          <t>15号屋</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -4698,23 +4701,27 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>5239</v>
+        <v>2695</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>322700000</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>61596</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4723,12 +4730,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4738,14 +4745,14 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>16号屋</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4764,7 +4771,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3336</v>
+        <v>3053</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4773,14 +4780,14 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>151080000</v>
+        <v>116800000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>45288</v>
+        <v>38257</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4811,7 +4818,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>17号屋</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4830,7 +4837,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2716</v>
+        <v>3059</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4881,7 +4888,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>15号屋</t>
+          <t>18号屋</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4900,27 +4907,23 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2695</v>
+        <v>5509</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>362500000</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>65801</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4929,12 +4932,12 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -4944,14 +4947,14 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>16号屋</t>
+          <t>19号屋</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4970,23 +4973,27 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>3053</v>
+        <v>3059</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>116800000</v>
-      </c>
-      <c r="I64" s="5" t="n">
-        <v>38257</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -5017,7 +5024,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>17号屋</t>
+          <t>20号屋</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -5036,27 +5043,23 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>3059</v>
+        <v>3436</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>40163</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -5065,12 +5068,12 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -5080,14 +5083,14 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>18号屋</t>
+          <t>21号屋</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -5106,7 +5109,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>5509</v>
+        <v>3297</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -5115,14 +5118,14 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>362500000</v>
+        <v>138700000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>65801</v>
+        <v>42069</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5153,7 +5156,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>19号屋</t>
+          <t>22号屋</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -5172,27 +5175,23 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>3059</v>
+        <v>3285</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>42009</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5223,7 +5222,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>20号屋</t>
+          <t>23号屋</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -5242,7 +5241,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>3436</v>
+        <v>3272</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5251,14 +5250,14 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>138000000</v>
+        <v>139988888</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>40163</v>
+        <v>42784</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5289,7 +5288,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>21号屋</t>
+          <t>25号屋</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -5308,7 +5307,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>3297</v>
+        <v>3289</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -5317,14 +5316,14 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>138700000</v>
+        <v>162820000</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>42069</v>
+        <v>49504</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -5355,7 +5354,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>22号屋</t>
+          <t>26号屋</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -5374,23 +5373,27 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>3285</v>
+        <v>3350</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>138000000</v>
-      </c>
-      <c r="I70" s="5" t="n">
-        <v>42009</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -5421,7 +5424,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>23号屋</t>
+          <t>27号屋</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -5440,7 +5443,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>3272</v>
+        <v>3304</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5449,14 +5452,14 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>139988888</v>
+        <v>146036800</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>42784</v>
+        <v>44200</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5487,7 +5490,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>25号屋</t>
+          <t>28号屋</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -5506,7 +5509,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>3289</v>
+        <v>5260</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5515,14 +5518,14 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>162820000</v>
+        <v>260341664</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>49504</v>
+        <v>49495</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5553,7 +5556,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26号屋</t>
+          <t>29号屋</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -5572,7 +5575,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>3350</v>
+        <v>3382</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5623,7 +5626,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>27号屋</t>
+          <t>30号屋</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -5642,7 +5645,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>3304</v>
+        <v>2738</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5651,14 +5654,14 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>146036800</v>
+        <v>107460000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>44200</v>
+        <v>39248</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5689,7 +5692,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>28号屋</t>
+          <t>31号屋</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -5708,7 +5711,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>5260</v>
+        <v>2739</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5717,14 +5720,14 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>260341664</v>
+        <v>96136000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>49495</v>
+        <v>35099</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5755,7 +5758,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>29号屋</t>
+          <t>32号屋</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -5774,11 +5777,11 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>3382</v>
+        <v>3063</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5788,12 +5791,12 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -5803,12 +5806,12 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -5818,14 +5821,14 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>30号屋</t>
+          <t>33号屋</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -5844,7 +5847,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>2738</v>
+        <v>3102</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5853,14 +5856,14 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>107460000</v>
+        <v>115238700</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>39248</v>
+        <v>37150</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5891,7 +5894,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>31号屋</t>
+          <t>35号屋</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -5910,7 +5913,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>2739</v>
+        <v>3102</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5919,14 +5922,14 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>96136000</v>
+        <v>115840200</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>35099</v>
+        <v>37344</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5957,7 +5960,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>32号屋</t>
+          <t>36号屋</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -5980,7 +5983,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -6027,7 +6030,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>33号屋</t>
+          <t>38号屋</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -6046,7 +6049,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>3102</v>
+        <v>4692</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -6055,14 +6058,14 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>115238700</v>
+        <v>256000000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>37150</v>
+        <v>54561</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6085,208 +6088,6 @@
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>35号屋</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>3102</v>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>115840200</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>37344</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L81" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M81" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N81" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>36号屋</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>3063</v>
-      </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N82" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>38号屋</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="n">
-        <v>4692</v>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="n">
-        <v>256000000</v>
-      </c>
-      <c r="I83" s="5" t="n">
-        <v>54561</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6302,186 +6103,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>8座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>A | 1170呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>B | 1215呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>1&amp;2</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>A | 2456呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>B | 2565呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>A | 1100呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1097呎 (3房)
-$2768万
-$25,232/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6608,7 +6229,7 @@
           <t>C | 2452呎 (4+房)
 $8776万
 $35,791/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -6616,7 +6237,7 @@
           <t>D | 2437呎 (4+房)
 $8223万
 $33,743/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6247,7 @@
           <t>G&amp;1</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 2436呎 (4+房)
 招标单位
@@ -6639,7 +6260,7 @@
           <t>B | 2436呎 (4+房)
 $8778万
 $36,034/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -6654,7 +6275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6714,7 +6335,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>33 套</t>
+          <t>34 套</t>
         </is>
       </c>
       <c r="B3" s="26" t="inlineStr">
@@ -6739,7 +6360,7 @@
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>7 套</t>
+          <t>8 套</t>
         </is>
       </c>
     </row>
@@ -6786,16 +6407,25 @@
           <t>第 1 行</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>1号屋
+7079呎 (3房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>2号屋
 4706呎 (4+房)
-(26年-07月)
+(26年-07月-06日)
 $2.68亿
 $56,949/呎</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>3号屋
 4662呎 (4+房)
@@ -6804,16 +6434,16 @@
 -</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>5号屋
 4666呎 (4+房)
-(26年-02月)
+(26年-02月-09日)
 $2.47亿
 $52,846/呎</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>6号屋
 4737呎 (4+房)
@@ -6822,7 +6452,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>7号屋
 4728呎 (4+房)
@@ -6831,7 +6461,14 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>第 2 行</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>8号屋
 6723呎 (4+房)
@@ -6840,14 +6477,7 @@
 暂无呎价</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>第 2 行</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>9号屋
 3601呎 (4+房)
@@ -6856,25 +6486,25 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>10号屋
 5239呎 (4+房)
-(25年-12月)
+(25年-12月-23日)
 $3.23亿
 $61,596/呎</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>11号屋
 3336呎 (4+房)
-(26年-07月)
+(26年-07月-19日)
 $1.51亿
 $45,288/呎</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>12号屋
 2716呎 (4+房)
@@ -6883,32 +6513,32 @@
 -</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>12座
 3212呎 (4+房)
-(26年-06月)
+(26年-06月-07日)
 $1.20亿
 $37,298/呎</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>第 3 行</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>12座
 3198呎 (4+房)
-(26年-05月)
+(26年-05月-18日)
 $1.28亿
 $39,950/呎</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>第 3 行</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>15号屋
 2695呎 (4+房)
@@ -6917,16 +6547,16 @@
 -</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>16号屋
 3053呎 (4+房)
-(26年-07月)
+(26年-07月-12日)
 $1.17亿
 $38,257/呎</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>17号屋
 3059呎 (4+房)
@@ -6935,16 +6565,16 @@
 -</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>18号屋
 5509呎 (4+房)
-(25年-12月)
+(25年-12月-23日)
 $3.62亿
 $65,801/呎</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>19号屋
 3059呎 (4+房)
@@ -6953,59 +6583,59 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>第 4 行</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>20号屋
 3436呎 (4+房)
-(25年-07月)
+(25年-07月-22日)
 $1.38亿
 $40,163/呎</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>第 4 行</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>21号屋
 3297呎 (4+房)
-(26年-04月)
+(26年-04月-22日)
 $1.39亿
 $42,069/呎</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>22号屋
 3285呎 (4+房)
-(25年-10月)
+(25年-10月-05日)
 $1.38亿
 $42,009/呎</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>23号屋
 3272呎 (4+房)
-(25年-09月)
+(25年-09月-03日)
 $1.40亿
 $42,784/呎</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>25号屋
 3289呎 (4+房)
-(26年-06月)
+(26年-06月-25日)
 $1.63亿
 $49,504/呎</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>26号屋
 3350呎 (4+房)
@@ -7014,32 +6644,32 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>27号屋
 3304呎 (4+房)
-(24年-06月)
+(24年-06月-24日)
 $1.46亿
 $44,200/呎</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>第 5 行</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>28号屋
 5260呎 (4+房)
-(25年-04月)
+(25年-04月-07日)
 $2.60亿
 $49,495/呎</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>29号屋
 3382呎 (4+房)
@@ -7048,25 +6678,25 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>30号屋
 2738呎 (4+房)
-(26年-02月)
+(26年-02月-12日)
 $1.07亿
 $39,248/呎</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>31号屋
 2739呎 (4+房)
-(24年-11月)
+(24年-11月-28日)
 $9,614万
 $35,099/呎</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>32号屋
 3063呎 (4+房)
@@ -7075,32 +6705,32 @@
 -</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>33号屋
 3102呎 (4+房)
-(24年-05月)
+(24年-05月-29日)
 $1.15亿
 $37,150/呎</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="80" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>35号屋
 3102呎 (4+房)
-(24年-05月)
+(24年-05月-13日)
 $1.16亿
 $37,344/呎</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>36号屋
 3063呎 (4+房)
@@ -7109,16 +6739,15 @@
 -</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>38号屋
 4692呎 (4+房)
-(25年-11月)
+(25年-11月-06日)
 $2.56亿
 $54,561/呎</t>
         </is>
       </c>
-      <c r="E11" s="31" t="inlineStr"/>
       <c r="F11" s="31" t="inlineStr"/>
       <c r="G11" s="31" t="inlineStr"/>
     </row>
@@ -7258,7 +6887,7 @@
           <t>C | 2452呎 (4+房)
 $8620万
 $35,155/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -7266,7 +6895,7 @@
           <t>D | 2551呎 (4+房)
 $8307万
 $32,564/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -7281,7 +6910,7 @@
           <t>A | 2466呎 (4+房)
 $17361万
 $70,403/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -7289,7 +6918,7 @@
           <t>B | 2466呎 (4+房)
 $17361万
 $70,403/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -7316,14 +6945,12 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>11座 销控网格图</t>
+          <t>1座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -7367,7 +6994,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7377,7 +7004,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7407,16 +7034,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -7424,22 +7041,20 @@
           <t>2&amp;3</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>C | 2566呎 (4+房)
-$9469万
-$36,900/呎
-(24年-08月)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 2437呎 (4+房)
-$8502万
-$34,887/呎
-(26年-05月)</t>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1931呎 (4+房)
+$6373万
+$33,002/呎
+(24年-05月-16日)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1851呎 (4+房)
+$7337万
+$39,638/呎
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -7451,22 +7066,20 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 2466呎 (4+房)
-$8412万
-$34,111/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>B | 2436呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
+          <t>A | 1826呎 (4+房)
+$5387万
+$29,502/呎
+(26年-03月-24日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1805呎 (4+房)
+$5315万
+$29,446/呎
+(24年-05月-13日)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7494,7 +7107,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>1座 销控网格图</t>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -7588,17 +7201,17 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t>A | 1931呎 (4+房)
-$6373万
-$33,002/呎
-(24年-05月)</t>
+$6083万
+$31,502/呎
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 1851呎 (4+房)
-$7337万
-$39,638/呎
-(26年-06月)</t>
+$6109万
+$33,003/呎
+(24年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -7611,17 +7224,17 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 1826呎 (4+房)
-$5387万
-$29,502/呎
-(26年-03月)</t>
+$5254万
+$28,773/呎
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 1805呎 (4+房)
-$5315万
-$29,446/呎
-(24年-05月)</t>
+$5533万
+$30,654/呎
+(25年-11月-24日)</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7651,7 +7264,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>2座 销控网格图</t>
+          <t>3座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -7690,32 +7303,32 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -7739,46 +7352,62 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>2&amp;3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1931呎 (4+房)
-$6083万
-$31,502/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 1851呎 (4+房)
-$6109万
-$33,003/呎
-(24年-05月)</t>
-        </is>
-      </c>
+          <t>A | 1871呎 (4+房)
+$6752万
+$36,086/呎
+(24年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>G&amp;1</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 1826呎 (4+房)
-$5254万
-$28,773/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 1805呎 (4+房)
-$5533万
-$30,654/呎
-(25年-11月)</t>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1874呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 1855呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>A | 844呎 (2房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 834呎 (2房)
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -7808,7 +7437,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>3座 销控网格图</t>
+          <t>5座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -7862,12 +7491,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -7899,15 +7528,15 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>A | 1871呎 (4+房)
-$6752万
-$36,086/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr"/>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 1871呎 (4+房)
+$7708万
+$41,197/呎
+(25年-02月-17日)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -7915,9 +7544,9 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>A | 1874呎 (4+房)
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1931呎 (4+房)
 -
 -
 (待售)</t>
@@ -7925,33 +7554,33 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>B | 1855呎 (4+房)
+          <t>B | 1910呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 844呎 (2房)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>A | 844呎 (2房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 834呎 (2房)
--
--
-(待售)</t>
+$2450万
+$29,376/呎
+(25年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7610,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>5座 销控网格图</t>
+          <t>6座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8020,32 +7649,32 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
     </row>
@@ -8072,13 +7701,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 1170呎 (3房)
+$4380万
+$37,440/呎
+(25年-07月-21日)</t>
+        </is>
+      </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 1871呎 (4+房)
-$7708万
-$41,197/呎
-(25年-02月)</t>
+          <t>B | 1171呎 (3房)
+$4382万
+$37,421/呎
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -8088,20 +7724,20 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>A | 1931呎 (4+房)
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2403呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>B | 1910呎 (4+房)
--
--
-(待售)</t>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 2511呎 (4+房)
+$6812万
+$27,129/呎
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -8111,20 +7747,20 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 844呎 (2房)
-招标单位
--
-(在售)</t>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 1100呎 (3房)
+$2860万
+$26,000/呎
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 834呎 (2房)
-$2450万
-$29,376/呎
-(25年-03月)</t>
+          <t>B | 1097呎 (3房)
+$3159万
+$28,801/呎
+(25年-03月-05日)</t>
         </is>
       </c>
     </row>
@@ -8154,7 +7790,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>6座 销控网格图</t>
+          <t>7座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8198,17 +7834,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8250,15 +7886,15 @@
           <t>A | 1170呎 (3房)
 $4380万
 $37,440/呎
-(25年-07月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 1171呎 (3房)
-$4382万
-$37,421/呎
-(26年-05月)</t>
+$4380万
+$37,404/呎
+(25年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -8268,7 +7904,7 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 2403呎 (4+房)
 -
@@ -8276,12 +7912,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 2511呎 (4+房)
-$6812万
-$27,129/呎
-(26年-05月)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -8294,17 +7930,17 @@
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 1100呎 (3房)
-$2860万
-$26,000/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
+$2911万
+$26,464/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 1097呎 (3房)
-$3159万
-$28,801/呎
-(25年-03月)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -8334,7 +7970,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>7座 销控网格图</t>
+          <t>8座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -8388,17 +8024,17 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
@@ -8425,20 +8061,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>A | 1170呎 (3房)
-$4380万
-$37,440/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (3房)
-$4380万
-$37,404/呎
-(25年-05月)</t>
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>B | 1215呎 (3房)
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -8448,9 +8084,9 @@
           <t>1&amp;2</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>A | 2403呎 (4+房)
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2456呎 (4+房)
 -
 -
 (待售)</t>
@@ -8458,10 +8094,10 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>B | 2511呎 (4+房)
-招标单位
+          <t>B | 2565呎 (4+房)
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -8471,20 +8107,20 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1100呎 (3房)
-$2911万
-$26,464/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1097呎 (3房)
-招标单位
--
-(在售)</t>
+$2768万
+$25,232/呎
+(26年-02月-23日)</t>
         </is>
       </c>
     </row>
